--- a/в бланки заводов/Останкино ЗПФ/ostankino_zpf/NV/moduls/1С.xlsx
+++ b/в бланки заводов/Останкино ЗПФ/ostankino_zpf/NV/moduls/1С.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино ЗПФ\ostankino_zpf\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{737CB7B6-D5AA-419F-8BF5-DF64C4C4EF41}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C02CA21E-B610-4F57-AE99-660650DFC5E5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$1</definedName>
   </definedNames>
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>1С</t>
   </si>
@@ -103,6 +106,48 @@
   </si>
   <si>
     <t>СОЧНЫЕ СО СЛ.МАСЛ.ПМ пельм пл.0.7кг зам.</t>
+  </si>
+  <si>
+    <t>6824 ОСТАНКИНСКИЕ пельм кор.0,5кг зам_NEW  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>7049 С КАРТОФ.И ГРИБ.вареники пл.0,42кг зам  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>7085 ОСТАНКИНСКИЕ пельм пл.0,7кг 10шт.зам  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>7212 СОЧНЫЕ Папа Может пельм пл.0,42кг зам  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>7214 СОЧНЫЕ Папа Может пельм пл.0,7кг зам  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>7224 МЯСНЫЕ ПРЕМИУМ пельм кор.0,4кг зам  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>7375 СОЧНЫЕ Папа Может пельм 4кг зам  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>ОСТАНКИНСКИЕ пельм кор.0.5кг зам_NEW</t>
+  </si>
+  <si>
+    <t>С КАРТОФ.И ГРИБ.вареники пл.0.42кг зам.</t>
+  </si>
+  <si>
+    <t>ОСТАНКИНСКИЕ пельм пл. 0.7кг 10шт.зам.</t>
+  </si>
+  <si>
+    <t>СОЧНЫЕ Папа Может пельм пл.0.42кг зам.</t>
+  </si>
+  <si>
+    <t>СОЧНЫЕ Папа Может пельм пл.0.7кг зам.</t>
+  </si>
+  <si>
+    <t>МЯСНЫЕ ПРЕМИУМ пельм кор.0.4кг зам.</t>
+  </si>
+  <si>
+    <t>СОЧНЫЕ Папа Может пельм 4кг зам.</t>
   </si>
 </sst>
 </file>
@@ -188,6 +233,344 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Бланк"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="D1">
+            <v>130133073</v>
+          </cell>
+          <cell r="E1" t="str">
+            <v xml:space="preserve">ЛП Луганск </v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="D3">
+            <v>46209</v>
+          </cell>
+          <cell r="E3" t="str">
+            <v xml:space="preserve">Доставка: </v>
+          </cell>
+          <cell r="F3">
+            <v>46212</v>
+          </cell>
+          <cell r="G3" t="str">
+            <v>Луганск</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="D6" t="str">
+            <v xml:space="preserve">Москва :  </v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="D7" t="str">
+            <v>Тип заказа:</v>
+          </cell>
+          <cell r="E7" t="str">
+            <v>ZOR</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="D9" t="str">
+            <v>Код материала</v>
+          </cell>
+          <cell r="E9" t="str">
+            <v>Заказ кг/шт</v>
+          </cell>
+          <cell r="F9" t="str">
+            <v>Вес нетто,  кг</v>
+          </cell>
+          <cell r="G9" t="str">
+            <v xml:space="preserve">Вес нетто,  кг </v>
+          </cell>
+          <cell r="H9" t="str">
+            <v>Вес нетто короба,      кг</v>
+          </cell>
+          <cell r="I9" t="str">
+            <v>Срок реализации, суток</v>
+          </cell>
+          <cell r="J9" t="str">
+            <v>Примечание</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="D12">
+            <v>1002134615897</v>
+          </cell>
+          <cell r="F12">
+            <v>0.42</v>
+          </cell>
+          <cell r="G12">
+            <v>0</v>
+          </cell>
+          <cell r="H12">
+            <v>4.2</v>
+          </cell>
+          <cell r="I12">
+            <v>120</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="D13">
+            <v>1002131166149</v>
+          </cell>
+          <cell r="F13">
+            <v>0.3</v>
+          </cell>
+          <cell r="G13">
+            <v>0</v>
+          </cell>
+          <cell r="H13">
+            <v>3.6</v>
+          </cell>
+          <cell r="I13">
+            <v>120</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="D14">
+            <v>1002134276819</v>
+          </cell>
+          <cell r="F14">
+            <v>0.3</v>
+          </cell>
+          <cell r="G14">
+            <v>0</v>
+          </cell>
+          <cell r="H14">
+            <v>3.6</v>
+          </cell>
+          <cell r="I14">
+            <v>120</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="D15">
+            <v>1002131186202</v>
+          </cell>
+          <cell r="F15">
+            <v>0.3</v>
+          </cell>
+          <cell r="G15">
+            <v>0</v>
+          </cell>
+          <cell r="H15">
+            <v>3.6</v>
+          </cell>
+          <cell r="I15">
+            <v>120</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="D16">
+            <v>1002133376148</v>
+          </cell>
+          <cell r="F16">
+            <v>0.3</v>
+          </cell>
+          <cell r="G16">
+            <v>0</v>
+          </cell>
+          <cell r="H16">
+            <v>3.6</v>
+          </cell>
+          <cell r="I16">
+            <v>120</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="D17">
+            <v>1002131146209</v>
+          </cell>
+          <cell r="F17">
+            <v>0.35</v>
+          </cell>
+          <cell r="G17">
+            <v>0</v>
+          </cell>
+          <cell r="H17">
+            <v>4.2</v>
+          </cell>
+          <cell r="I17">
+            <v>120</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="D18">
+            <v>1002131156168</v>
+          </cell>
+          <cell r="F18">
+            <v>0.35</v>
+          </cell>
+          <cell r="G18">
+            <v>0</v>
+          </cell>
+          <cell r="H18">
+            <v>4.2</v>
+          </cell>
+          <cell r="I18">
+            <v>120</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="D19">
+            <v>1002134275579</v>
+          </cell>
+          <cell r="F19">
+            <v>0.42</v>
+          </cell>
+          <cell r="G19">
+            <v>0</v>
+          </cell>
+          <cell r="H19">
+            <v>4.2</v>
+          </cell>
+          <cell r="I19">
+            <v>120</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="D20">
+            <v>1002131155754</v>
+          </cell>
+          <cell r="F20">
+            <v>4.5</v>
+          </cell>
+          <cell r="G20">
+            <v>0</v>
+          </cell>
+          <cell r="H20">
+            <v>4.5</v>
+          </cell>
+          <cell r="I20">
+            <v>120</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="D21">
+            <v>1002131185755</v>
+          </cell>
+          <cell r="F21">
+            <v>4.5</v>
+          </cell>
+          <cell r="G21">
+            <v>0</v>
+          </cell>
+          <cell r="H21">
+            <v>4.5</v>
+          </cell>
+          <cell r="I21">
+            <v>120</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="D23">
+            <v>1002116437216</v>
+          </cell>
+          <cell r="F23">
+            <v>0.7</v>
+          </cell>
+          <cell r="G23">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="D24">
+            <v>1002112606824</v>
+          </cell>
+          <cell r="F24">
+            <v>0.5</v>
+          </cell>
+          <cell r="G24">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="D25">
+            <v>1002151787049</v>
+          </cell>
+          <cell r="F25">
+            <v>0.42</v>
+          </cell>
+          <cell r="G25">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="D26">
+            <v>1002112607085</v>
+          </cell>
+          <cell r="F26">
+            <v>0.7</v>
+          </cell>
+          <cell r="G26">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="D27">
+            <v>1002112857212</v>
+          </cell>
+          <cell r="F27">
+            <v>0.42</v>
+          </cell>
+          <cell r="G27">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="D28">
+            <v>1002112857214</v>
+          </cell>
+          <cell r="F28">
+            <v>0.7</v>
+          </cell>
+          <cell r="G28">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="D29">
+            <v>1002116517224</v>
+          </cell>
+          <cell r="F29">
+            <v>0.4</v>
+          </cell>
+          <cell r="G29">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="D30">
+            <v>1002112857375</v>
+          </cell>
+          <cell r="F30">
+            <v>1</v>
+          </cell>
+          <cell r="G30">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="E31">
+            <v>0</v>
+          </cell>
+          <cell r="G31">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -453,18 +836,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.7109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="16.42578125" style="3" customWidth="1"/>
     <col min="3" max="3" width="49.140625" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" customWidth="1"/>
     <col min="5" max="5" width="17.5703125" customWidth="1"/>
     <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -475,7 +858,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -485,8 +868,12 @@
       <c r="C2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="3">
+        <f>VLOOKUP(B2,[1]Бланк!$D:$J,1,0)</f>
+        <v>1002134275579</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -496,8 +883,12 @@
       <c r="C3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" s="3">
+        <f>VLOOKUP(B3,[1]Бланк!$D:$J,1,0)</f>
+        <v>1002131155754</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -507,8 +898,12 @@
       <c r="C4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" s="3">
+        <f>VLOOKUP(B4,[1]Бланк!$D:$J,1,0)</f>
+        <v>1002131185755</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -518,8 +913,12 @@
       <c r="C5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" s="3">
+        <f>VLOOKUP(B5,[1]Бланк!$D:$J,1,0)</f>
+        <v>1002134615897</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -529,8 +928,12 @@
       <c r="C6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" s="3">
+        <f>VLOOKUP(B6,[1]Бланк!$D:$J,1,0)</f>
+        <v>1002133376148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -540,8 +943,12 @@
       <c r="C7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" s="3">
+        <f>VLOOKUP(B7,[1]Бланк!$D:$J,1,0)</f>
+        <v>1002131166149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -551,8 +958,12 @@
       <c r="C8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" s="3">
+        <f>VLOOKUP(B8,[1]Бланк!$D:$J,1,0)</f>
+        <v>1002131156168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -562,8 +973,12 @@
       <c r="C9" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" s="3">
+        <f>VLOOKUP(B9,[1]Бланк!$D:$J,1,0)</f>
+        <v>1002131186202</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
@@ -573,8 +988,12 @@
       <c r="C10" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" s="3">
+        <f>VLOOKUP(B10,[1]Бланк!$D:$J,1,0)</f>
+        <v>1002131146209</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -584,8 +1003,12 @@
       <c r="C11" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" s="3">
+        <f>VLOOKUP(B11,[1]Бланк!$D:$J,1,0)</f>
+        <v>1002134276819</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -594,6 +1017,115 @@
       </c>
       <c r="C12" t="s">
         <v>22</v>
+      </c>
+      <c r="D12" s="3">
+        <f>VLOOKUP(B12,[1]Бланк!$D:$J,1,0)</f>
+        <v>1002116437216</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1002112606824</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="3">
+        <f>VLOOKUP(B13,[1]Бланк!$D:$J,1,0)</f>
+        <v>1002112606824</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1002151787049</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="3">
+        <f>VLOOKUP(B14,[1]Бланк!$D:$J,1,0)</f>
+        <v>1002151787049</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="3">
+        <v>1002112607085</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="3">
+        <f>VLOOKUP(B15,[1]Бланк!$D:$J,1,0)</f>
+        <v>1002112607085</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="3">
+        <v>1002112857212</v>
+      </c>
+      <c r="C16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="3">
+        <f>VLOOKUP(B16,[1]Бланк!$D:$J,1,0)</f>
+        <v>1002112857212</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="3">
+        <v>1002112857214</v>
+      </c>
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="3">
+        <f>VLOOKUP(B17,[1]Бланк!$D:$J,1,0)</f>
+        <v>1002112857214</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1002116517224</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="3">
+        <f>VLOOKUP(B18,[1]Бланк!$D:$J,1,0)</f>
+        <v>1002116517224</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="3">
+        <v>1002112857375</v>
+      </c>
+      <c r="C19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="3">
+        <f>VLOOKUP(B19,[1]Бланк!$D:$J,1,0)</f>
+        <v>1002112857375</v>
       </c>
     </row>
   </sheetData>
